--- a/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/createWorkoutSession-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/it/workout-session-service/createWorkoutSession-it-form.xlsx
@@ -315,7 +315,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14235112" cy="4624387"/>
+    <xdr:ext cx="15963900" cy="5105400"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -797,10 +797,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="26" width="11" customWidth="1"/>
+    <col min="1" max="29" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -826,6 +826,9 @@
     <row r="21" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="16" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
